--- a/results/link-prediction-gcn/Link/3shot/Cora/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/3shot/Cora/GCN_total_results.xlsx
@@ -903,447 +903,447 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>0.4760±0.0019</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.4873±0.0125</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4839±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.6050±0.0213</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.6053±0.0329</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.6053±0.0329</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.6053±0.0329</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.6271±0.0054</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5338±0.0429</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5961±0.0391</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.6034±0.0000</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.6480±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.6480±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.6480±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.6328±0.0000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5332±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.6433±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.6300±0.0229</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.4940±0.0060</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5354±0.0245</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.4896±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.5028±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.6632±0.0399</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5231±0.0313</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5231±0.0313</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5231±0.0313</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6739±0.0176</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.6657±0.0448</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.5259±0.0353</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.5054±0.0439</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4826±0.0126</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.5164±0.0235</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.6366±0.0000</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5974±0.0689</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5825±0.0584</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.5825±0.0584</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.5825±0.0584</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5933±0.0660</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.6531±0.0163</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.5743±0.0529</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.5373±0.0342</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6135±0.0461</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4766±0.0037</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5253±0.0140</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.5013±0.0018</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6768±0.0068</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6660±0.0217</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6660±0.0217</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6660±0.0217</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6553±0.0247</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6799±0.0079</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6616±0.0202</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.5180±0.0667</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.7154±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.5202±0.0121</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.6170±0.0151</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5971±0.0287</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5971±0.0287</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5971±0.0287</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5803±0.0583</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6531±0.0413</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.5961±0.0227</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.4962±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.4962±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.4810±0.0129</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.5073±0.0131</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.6404±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.6404±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.6404±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0.5772±0.0547</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.5620±0.0439</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.5620±0.0439</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.5620±0.0439</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.5863±0.0621</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.5677±0.0155</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.5661±0.0496</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.5920±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.6328±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.4725±0.0000</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.6300±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4972±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.5142±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.4905±0.0119</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.5183±0.0197</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.6879±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.6964±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.6964±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.6964±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.7021±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.6528±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.7011±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.4772±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.6006±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.6006±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.6006±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.5702±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.6252±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.4981±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.6328±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.6328±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.6328±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.6167±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.4877±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4801±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.6385±0.0000</t>
+          <t>0.5085±0.0058</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5047±0.0000</t>
+          <t>0.5104±0.0046</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5047±0.0000</t>
+          <t>0.5104±0.0046</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5047±0.0000</t>
+          <t>0.5104±0.0046</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5047±0.0000</t>
+          <t>0.5123±0.0148</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.6546±0.0000</t>
+          <t>0.5762±0.0117</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5047±0.0000</t>
+          <t>0.5098±0.0057</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0000±0.0000</t>
+          <t>0.6667±0.0000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1365,447 +1365,447 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>0.6390±0.0040</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6448±0.0140</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.6486±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.6802±0.0094</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6893±0.0089</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6893±0.0089</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6893±0.0089</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6894±0.0136</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6559±0.0031</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.6854±0.0166</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.6980±0.0000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.7204±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.7204±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.7204±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.6877±0.0000</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6476±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.7173±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.7093±0.0073</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6526±0.0069</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6676±0.0147</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6542±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6606±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7381±0.0174</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6762±0.0129</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6762±0.0129</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6762±0.0129</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7417±0.0070</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7403±0.0194</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6776±0.0149</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.6016±0.0502</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6462±0.0145</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6531±0.0070</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.7258±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6837±0.0131</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6762±0.0131</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6762±0.0131</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6762±0.0131</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6786±0.0096</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7262±0.0056</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6734±0.0146</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.3196±0.2318</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.7159±0.0234</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6382±0.0044</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6497±0.0103</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6672±0.0008</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7400±0.0092</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7382±0.0085</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7382±0.0085</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7382±0.0085</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7303±0.0108</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7420±0.0059</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7340±0.0125</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6126±0.0636</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7699±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6571±0.0131</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6695±0.0137</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6905±0.0093</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6905±0.0093</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6905±0.0093</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6751±0.0085</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7364±0.0204</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6701±0.0123</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.2222±0.3143</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6633±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6585±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6438±0.0130</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6640±0.0019</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.6717±0.0040</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6739±0.0053</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6739±0.0053</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6739±0.0053</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.6754±0.0109</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6840±0.0114</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6722±0.0044</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.7004±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.7004±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.7004±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.7034±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.6979±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.6380±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.7277±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6637±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6545±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6415±0.0120</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6510±0.0190</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7509±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7601±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7601±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7601±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7588±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7363±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7630±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6658±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6363±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6618±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6618±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6618±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6962±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6776±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6650±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.7012±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.7012±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.7012±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6662±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6897±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6662±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6512±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.6418±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.7176±0.0000</t>
+          <t>0.6704±0.0025</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6688±0.0000</t>
+          <t>0.6713±0.0021</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6688±0.0000</t>
+          <t>0.6713±0.0021</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6688±0.0000</t>
+          <t>0.6713±0.0021</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6688±0.0000</t>
+          <t>0.6720±0.0064</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7234±0.0000</t>
+          <t>0.6987±0.0055</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6688±0.0000</t>
+          <t>0.6708±0.0030</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6513±0.0000</t>
+          <t>0.5709±0.0139</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6683±0.0000</t>
+          <t>0.6709±0.0252</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5693±0.0000</t>
+          <t>0.6341±0.0283</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6391±0.0000</t>
+          <t>0.6387±0.0175</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6776±0.0000</t>
+          <t>0.6824±0.0135</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.6960±0.0000</t>
+          <t>0.6762±0.0117</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6510±0.0000</t>
+          <t>0.6815±0.0208</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7305±0.0000</t>
+          <t>0.7198±0.0292</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7305±0.0000</t>
+          <t>0.7198±0.0292</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7305±0.0000</t>
+          <t>0.7198±0.0292</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.6963±0.0000</t>
+          <t>0.7080±0.0205</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6018±0.0000</t>
+          <t>0.6418±0.0286</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7198±0.0000</t>
+          <t>0.7028±0.0380</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.4376±0.0000</t>
+          <t>0.5281±0.0669</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7634±0.0000</t>
+          <t>0.7474±0.0294</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.5012±0.0000</t>
+          <t>0.6044±0.0390</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.5246±0.0000</t>
+          <t>0.6671±0.0206</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6759±0.0000</t>
+          <t>0.6746±0.0085</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6518±0.0000</t>
+          <t>0.6799±0.0062</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.8056±0.0000</t>
+          <t>0.7939±0.0127</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7998±0.0000</t>
+          <t>0.8078±0.0083</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7998±0.0000</t>
+          <t>0.8078±0.0083</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7998±0.0000</t>
+          <t>0.8078±0.0083</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.8282±0.0000</t>
+          <t>0.7877±0.0083</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8574±0.0000</t>
+          <t>0.8224±0.0110</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7818±0.0000</t>
+          <t>0.7842±0.0134</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.4992±0.0000</t>
+          <t>0.5331±0.0321</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.6465±0.0000</t>
+          <t>0.6789±0.0218</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.6358±0.0000</t>
+          <t>0.6325±0.0192</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.6531±0.0000</t>
+          <t>0.6523±0.0224</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.6767±0.0000</t>
+          <t>0.6738±0.0147</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.6677±0.0000</t>
+          <t>0.6759±0.0144</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.6528±0.0000</t>
+          <t>0.6983±0.0046</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.6851±0.0000</t>
+          <t>0.6478±0.0218</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.6851±0.0000</t>
+          <t>0.6478±0.0218</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.6851±0.0000</t>
+          <t>0.6478±0.0218</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.6540±0.0000</t>
+          <t>0.6881±0.0068</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.7967±0.0000</t>
+          <t>0.7927±0.0131</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.6764±0.0000</t>
+          <t>0.6552±0.0241</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.4859±0.0000</t>
+          <t>0.5499±0.0054</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.8195±0.0000</t>
+          <t>0.7819±0.0373</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4895±0.0000</t>
+          <t>0.6311±0.0159</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.6490±0.0000</t>
+          <t>0.6748±0.0073</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.6748±0.0000</t>
+          <t>0.7165±0.0159</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6686±0.0000</t>
+          <t>0.6885±0.0075</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.8286±0.0000</t>
+          <t>0.7856±0.0286</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.8643±0.0000</t>
+          <t>0.7993±0.0016</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.8643±0.0000</t>
+          <t>0.7993±0.0016</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.8643±0.0000</t>
+          <t>0.7993±0.0016</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.8225±0.0000</t>
+          <t>0.7728±0.0196</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.8384±0.0000</t>
+          <t>0.8168±0.0240</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.8547±0.0000</t>
+          <t>0.7790±0.0210</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.5718±0.0000</t>
+          <t>0.5892±0.0606</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.6686±0.0000</t>
+          <t>0.6890±0.0151</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.6324±0.0000</t>
+          <t>0.6412±0.0273</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6548±0.0000</t>
+          <t>0.6675±0.0344</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6767±0.0000</t>
+          <t>0.6751±0.0131</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.6838±0.0000</t>
+          <t>0.6749±0.0111</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.6689±0.0000</t>
+          <t>0.6796±0.0107</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.6592±0.0000</t>
+          <t>0.6974±0.0060</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.6592±0.0000</t>
+          <t>0.6974±0.0060</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.6592±0.0000</t>
+          <t>0.6974±0.0060</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.6713±0.0000</t>
+          <t>0.6838±0.0127</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.7831±0.0000</t>
+          <t>0.8254±0.0039</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.6588±0.0000</t>
+          <t>0.6648±0.0135</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.5303±0.0000</t>
+          <t>0.5548±0.0733</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.6694±0.0000</t>
+          <t>0.6976±0.0159</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.6303±0.0000</t>
+          <t>0.6291±0.0321</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6426±0.0000</t>
+          <t>0.6404±0.0391</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.6751±0.0000</t>
+          <t>0.6774±0.0118</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.6762±0.0000</t>
+          <t>0.6791±0.0121</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.6848±0.0000</t>
+          <t>0.6695±0.0069</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.6943±0.0000</t>
+          <t>0.6582±0.0082</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.6943±0.0000</t>
+          <t>0.6582±0.0082</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.6943±0.0000</t>
+          <t>0.6582±0.0082</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.6891±0.0000</t>
+          <t>0.6829±0.0107</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6755±0.0000</t>
+          <t>0.7572±0.0349</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.6736±0.0000</t>
+          <t>0.6626±0.0151</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.5571±0.0000</t>
+          <t>0.5601±0.0262</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7078±0.0000</t>
+          <t>0.7503±0.0227</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4857±0.0000</t>
+          <t>0.6123±0.0187</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4912±0.0000</t>
+          <t>0.6298±0.0524</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.6864±0.0000</t>
+          <t>0.6718±0.0149</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.6249±0.0000</t>
+          <t>0.6540±0.0237</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7684±0.0000</t>
+          <t>0.7889±0.0091</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7916±0.0000</t>
+          <t>0.7511±0.0114</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7916±0.0000</t>
+          <t>0.7511±0.0114</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7916±0.0000</t>
+          <t>0.7511±0.0114</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7865±0.0000</t>
+          <t>0.7702±0.0148</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7619±0.0000</t>
+          <t>0.7727±0.0021</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7755±0.0000</t>
+          <t>0.7158±0.0040</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7092±0.0000</t>
+          <t>0.6093±0.0094</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7156±0.0000</t>
+          <t>0.6997±0.0279</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5553±0.0000</t>
+          <t>0.6735±0.0487</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6841±0.0000</t>
+          <t>0.6698±0.0164</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.7141±0.0000</t>
+          <t>0.7022±0.0150</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7263±0.0000</t>
+          <t>0.7020±0.0235</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6550±0.0000</t>
+          <t>0.6752±0.0171</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7286±0.0000</t>
+          <t>0.7103±0.0359</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7286±0.0000</t>
+          <t>0.7103±0.0359</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7286±0.0000</t>
+          <t>0.7103±0.0359</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6905±0.0000</t>
+          <t>0.6981±0.0195</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.6440±0.0000</t>
+          <t>0.6859±0.0171</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7059±0.0000</t>
+          <t>0.6954±0.0383</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.5264±0.0000</t>
+          <t>0.5774±0.0438</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7701±0.0000</t>
+          <t>0.7372±0.0319</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5019±0.0000</t>
+          <t>0.6122±0.0624</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.6554±0.0319</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7107±0.0000</t>
+          <t>0.6873±0.0165</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6977±0.0000</t>
+          <t>0.7034±0.0149</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7859±0.0000</t>
+          <t>0.7798±0.0163</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7900±0.0000</t>
+          <t>0.7988±0.0044</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7900±0.0000</t>
+          <t>0.7988±0.0044</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7900±0.0000</t>
+          <t>0.7988±0.0044</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.8221±0.0000</t>
+          <t>0.7796±0.0091</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8398±0.0000</t>
+          <t>0.8058±0.0136</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7618±0.0000</t>
+          <t>0.7595±0.0025</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.5604±0.0000</t>
+          <t>0.5839±0.0294</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.7010±0.0000</t>
+          <t>0.7102±0.0180</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6278±0.0000</t>
+          <t>0.6786±0.0275</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6818±0.0000</t>
+          <t>0.6941±0.0274</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7106±0.0000</t>
+          <t>0.6963±0.0203</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.7022±0.0000</t>
+          <t>0.6966±0.0188</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.7053±0.0000</t>
+          <t>0.7043±0.0099</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.6804±0.0000</t>
+          <t>0.6542±0.0012</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.6804±0.0000</t>
+          <t>0.6542±0.0012</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.6804±0.0000</t>
+          <t>0.6542±0.0012</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.7053±0.0000</t>
+          <t>0.6997±0.0231</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8082±0.0000</t>
+          <t>0.8018±0.0128</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6629±0.0105</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.5616±0.0000</t>
+          <t>0.6058±0.0172</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.8245±0.0000</t>
+          <t>0.7805±0.0242</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4947±0.0000</t>
+          <t>0.6597±0.0373</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.6264±0.0000</t>
+          <t>0.7003±0.0089</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.7105±0.0000</t>
+          <t>0.7263±0.0074</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7078±0.0000</t>
+          <t>0.7075±0.0148</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.8250±0.0000</t>
+          <t>0.7702±0.0301</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.8514±0.0000</t>
+          <t>0.7843±0.0052</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.8514±0.0000</t>
+          <t>0.7843±0.0052</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.8514±0.0000</t>
+          <t>0.7843±0.0052</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.8208±0.0000</t>
+          <t>0.7619±0.0233</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.8372±0.0000</t>
+          <t>0.8151±0.0136</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.8349±0.0000</t>
+          <t>0.7545±0.0233</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6434±0.0000</t>
+          <t>0.6365±0.0311</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7160±0.0000</t>
+          <t>0.7109±0.0165</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.6577±0.0000</t>
+          <t>0.6837±0.0404</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6988±0.0000</t>
+          <t>0.6981±0.0379</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7125±0.0000</t>
+          <t>0.6975±0.0182</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7184±0.0000</t>
+          <t>0.7028±0.0191</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7144±0.0000</t>
+          <t>0.6767±0.0085</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6606±0.0000</t>
+          <t>0.6913±0.0063</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6606±0.0000</t>
+          <t>0.6913±0.0063</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6606±0.0000</t>
+          <t>0.6913±0.0063</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7159±0.0000</t>
+          <t>0.6844±0.0111</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7845±0.0000</t>
+          <t>0.8094±0.0063</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.6494±0.0000</t>
+          <t>0.6617±0.0206</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.5691±0.0000</t>
+          <t>0.5838±0.0603</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7176±0.0000</t>
+          <t>0.7123±0.0174</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6465±0.0000</t>
+          <t>0.6634±0.0510</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6866±0.0000</t>
+          <t>0.6777±0.0434</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7107±0.0000</t>
+          <t>0.7001±0.0187</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7115±0.0000</t>
+          <t>0.7026±0.0208</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7243±0.0000</t>
+          <t>0.6692±0.0110</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.6860±0.0000</t>
+          <t>0.6674±0.0113</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.6860±0.0000</t>
+          <t>0.6674±0.0113</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.6860±0.0000</t>
+          <t>0.6674±0.0113</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7277±0.0000</t>
+          <t>0.6820±0.0050</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7199±0.0000</t>
+          <t>0.7808±0.0301</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.6604±0.0000</t>
+          <t>0.6660±0.0222</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.5989±0.0000</t>
+          <t>0.5975±0.0158</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7373±0.0000</t>
+          <t>0.7561±0.0263</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4928±0.0000</t>
+          <t>0.5992±0.0254</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.4960±0.0000</t>
+          <t>0.6202±0.0607</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.7195±0.0000</t>
+          <t>0.6927±0.0206</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6352±0.0000</t>
+          <t>0.6718±0.0164</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7524±0.0000</t>
+          <t>0.7778±0.0140</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7713±0.0000</t>
+          <t>0.7112±0.0183</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7713±0.0000</t>
+          <t>0.7112±0.0183</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7713±0.0000</t>
+          <t>0.7112±0.0183</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7860±0.0000</t>
+          <t>0.7600±0.0173</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7708±0.0000</t>
+          <t>0.7528±0.0066</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7231±0.0000</t>
+          <t>0.6711±0.0277</t>
         </is>
       </c>
     </row>
